--- a/rules/CORE-000745/negative/01/data/unit-test-coreid-FB0915-negative.xlsx
+++ b/rules/CORE-000745/negative/01/data/unit-test-coreid-FB0915-negative.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Library" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Validation" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="oi.xpt" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Library" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oi.xpt" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -49,7 +49,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -71,6 +71,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -116,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -139,6 +145,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -585,7 +595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -617,6 +627,220 @@
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Error value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>oi.xpt</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>OIPARMCD</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>oi.xpt</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>OIPARM</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Genotype</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>oi.xpt</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>OIPARMCD</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>GENTYPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>oi.xpt</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>OIPARM</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Genotype</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>oi.xpt</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>OIPARMCD</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SUBTYPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>oi.xpt</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>OIPARM</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>oi.xpt</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>OIPARMCD</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SUBTYPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>oi.xpt</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>9</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>OIPARM</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Subtype</t>
         </is>
       </c>
     </row>
@@ -790,12 +1014,12 @@
       <c r="D5" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
@@ -823,8 +1047,8 @@
       <c r="D6" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="10" t="n"/>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>Genotype</t>
         </is>
@@ -852,12 +1076,12 @@
       <c r="D7" t="n">
         <v>3</v>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>GENTYPE</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t>Genotype</t>
         </is>
@@ -885,12 +1109,12 @@
       <c r="D8" t="n">
         <v>4</v>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>SUBTYPE</t>
         </is>
       </c>
-      <c r="F8" s="8" t="n"/>
+      <c r="F8" s="13" t="n"/>
       <c r="G8" s="11" t="inlineStr">
         <is>
           <t>xxxxx</t>
@@ -914,12 +1138,12 @@
       <c r="D9" t="n">
         <v>5</v>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>SUBTYPE</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>Subtype</t>
         </is>
